--- a/naver-place-crawler/results_health/강화군_PT.xlsx
+++ b/naver-place-crawler/results_health/강화군_PT.xlsx
@@ -417,22 +417,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V6"/>
+  <dimension ref="A1:V23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
-    <col width="31" customWidth="1" min="8" max="8"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="10" customWidth="1" min="12" max="12"/>
-    <col width="34" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="10" customWidth="1" min="14" max="14"/>
     <col width="10" customWidth="1" min="15" max="15"/>
     <col width="10" customWidth="1" min="16" max="16"/>
@@ -581,7 +581,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천 강화군 강화읍 남문로 14 3층</t>
+          <t>인천광역시 강화군 강화읍 남문로 14 3층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -606,14 +606,10 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>https://talk.naver.com/ct/w4ri4t</t>
-        </is>
-      </c>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>X</t>
@@ -628,10 +624,10 @@
         <v>203</v>
       </c>
       <c r="Q2" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="R2" t="n">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -650,7 +646,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
@@ -662,29 +658,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>우리동네 헬스\u002FPT</t>
+          <t>에스오짐2호점</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dyj05180@naver.com</t>
+          <t>topten0@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>032-937-9870</t>
+          <t>032-934-2124</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천 강화군 불은면 강화동로 587 1층</t>
+          <t>인천광역시 강화군 강화읍 중앙로 27 3층 S.O GYM 2호점</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/sogym_official2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -694,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -715,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>14</v>
+        <v>139</v>
       </c>
       <c r="Q3" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R3" t="n">
-        <v>15</v>
+        <v>151</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -734,51 +730,51 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2084651240</t>
+          <t>1935773088</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084651240</t>
+          <t>https://m.place.naver.com/place/1935773088</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>몸짱휘트니스클럽</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>byy333@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0507-1419-9688</t>
+          <t>070-8039-5429</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천 강화군 선원면 중앙로 154 2충</t>
+          <t>인천광역시 강화군 송해면 당산리</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/byy333</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -788,12 +784,12 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -813,13 +809,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S4" t="inlineStr">
         <is>
@@ -828,46 +824,46 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>21494529</t>
+          <t>1877492123</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21494529</t>
+          <t>https://m.place.naver.com/place/1877492123</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>맥스 PT&amp;GT</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0507-1407-5359</t>
+          <t>070-8039-5430</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천 강화군 강화읍 동문안길 9-1 4층</t>
+          <t>인천광역시 강화군 양도면 건평리</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -910,10 +906,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -922,46 +918,46 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1296569152</t>
+          <t>1176255107</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296569152</t>
+          <t>https://m.place.naver.com/place/1176255107</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>맥스휘트니스클럽. 맥스PT샵</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>on180102@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0507-1327-2830</t>
+          <t>070-8039-5432</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천 강화군 강화읍 동문안길 9-1 4층</t>
+          <t>인천광역시 강화군 하점면 망월리</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1001,32 +997,1626 @@
         </is>
       </c>
       <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1299094791</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1299094791</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>맥스휘트니스클럽. 맥스PT샵</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>on180102@naver.com</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0507-1327-2830</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 동문안길 9-1 4층</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P7" t="n">
         <v>6</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="Q7" t="n">
         <v>6</v>
       </c>
-      <c r="R6" t="n">
+      <c r="R7" t="n">
         <v>12</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>X</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
         <is>
           <t>1506476586</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>https://m.place.naver.com/place/1506476586</t>
         </is>
       </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>070-8039-5423</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 갑곳리</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P8" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>1533095100</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1533095100</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>에스오짐 1호점</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0507-1381-0814</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 강화대로 199 2층</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P9" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>11</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>1342561169</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1342561169</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>에이스짐</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>acegym2@naver.com</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 강화대로404번길 7 3층</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>https://instagram.com/ace__gym?igshid=ye2mgag95d7j</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="P10" t="n">
+        <v>23</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>15</v>
+      </c>
+      <c r="R10" t="n">
+        <v>38</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1768451605</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1768451605</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>070-5255-2005</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 선원면 금월리</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>1147666750</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1147666750</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>070-8039-5426</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 불은면 고능리</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P12" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1663184692</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1663184692</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>스포츠시설</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>맥스 PT&amp;GT</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>topten0@naver.com</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0507-1407-5359</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 동문안길 9-1 4층</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>1</v>
+      </c>
+      <c r="R13" t="n">
+        <v>1</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>1296569152</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1296569152</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>전문건설업</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>070-8055-2327</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 길상면 길직리</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P14" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>1792485335</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1792485335</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>건축,토목</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>피티아시바</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>unixgaseol7@naver.com</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>070-5255-6620</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 하점면 신봉리</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>1018631235</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1018631235</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>070-8039-5427</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 서도면 말도리</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>1817432438</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1817432438</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>070-8039-5428</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 선원면 금월리</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>1944891267</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1944891267</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>070-8039-5431</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 양사면 교산리</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>1750263858</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1750263858</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>우리동네 헬스/PT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>subgymasan@naver.com</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>032-937-9870</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 불은면 강화동로 587 1층</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P19" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>1</v>
+      </c>
+      <c r="R19" t="n">
+        <v>15</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>2084651240</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/2084651240</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>장비,기기</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>hnco@naver.com</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>070-8039-5424</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 길상면 길직리</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>1236022169</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1236022169</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>스카이헬스클럽</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>rokmc9160@naver.com</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0507-1468-7831</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 강화읍 관청길23번길 8 관청길23번길8 스카이헬스클럽</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P21" t="n">
+        <v>6</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>17</v>
+      </c>
+      <c r="R21" t="n">
+        <v>23</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>11847161</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/11847161</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>소프트웨어개발</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>비즈픽스</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>breezessol@naver.com</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>031-987-8937</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>경기도 김포시 월곶면 김포대학로 22</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>1342017021</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/1342017021</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>헬스장</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>몸짱휘트니스클럽</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>byy333@naver.com</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0507-1419-9688</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>인천광역시 강화군 선원면 중앙로 154 2충</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>https://blog.naver.com/byy333</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="P23" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>3</v>
+      </c>
+      <c r="R23" t="n">
+        <v>10</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>X</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>21494529</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>https://m.place.naver.com/place/21494529</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>2026-04-28</t>
         </is>
       </c>
     </row>

--- a/naver-place-crawler/results_health/강화군_PT.xlsx
+++ b/naver-place-crawler/results_health/강화군_PT.xlsx
@@ -559,34 +559,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>위너핏</t>
+          <t>맥스휘트니스클럽. 맥스PT샵</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>boos66@naver.com</t>
+          <t>on180102@naver.com</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0507-1476-1622</t>
+          <t>0507-1327-2830</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 남문로 14 3층</t>
+          <t>인천광역시 강화군 강화읍 동문안길 9-1 4층</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/boos66</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -596,12 +596,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -617,17 +617,17 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P2" t="n">
-        <v>203</v>
+        <v>6</v>
       </c>
       <c r="Q2" t="n">
-        <v>294</v>
+        <v>6</v>
       </c>
       <c r="R2" t="n">
-        <v>497</v>
+        <v>12</v>
       </c>
       <c r="S2" t="inlineStr">
         <is>
@@ -636,12 +636,12 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1895477243</t>
+          <t>1506476586</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1895477243</t>
+          <t>https://m.place.naver.com/place/1506476586</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -653,34 +653,34 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>에스오짐2호점</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
-          <t>032-934-2124</t>
+          <t>070-8039-5427</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 중앙로 27 3층 S.O GYM 2호점</t>
+          <t>인천광역시 강화군 서도면 말도리</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://instagram.com/sogym_official2</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -690,7 +690,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -711,17 +711,17 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P3" t="n">
-        <v>139</v>
+        <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="S3" t="inlineStr">
         <is>
@@ -730,12 +730,12 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>1935773088</t>
+          <t>1817432438</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1935773088</t>
+          <t>https://m.place.naver.com/place/1817432438</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -757,19 +757,19 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
-          <t>070-8039-5429</t>
+          <t>070-8039-5430</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 송해면 당산리</t>
+          <t>인천광역시 강화군 양도면 건평리</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -824,12 +824,12 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>1877492123</t>
+          <t>1176255107</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1877492123</t>
+          <t>https://m.place.naver.com/place/1176255107</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -841,29 +841,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>에스오짐 1호점</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>topten0@naver.com</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
-          <t>070-8039-5430</t>
+          <t>0507-1381-0814</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 양도면 건평리</t>
+          <t>인천광역시 강화군 강화읍 강화대로 199 2층</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -903,13 +903,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="S5" t="inlineStr">
         <is>
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>1176255107</t>
+          <t>1342561169</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1176255107</t>
+          <t>https://m.place.naver.com/place/1342561169</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -935,29 +935,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
-          <t>070-8039-5432</t>
+          <t>070-5255-2005</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 하점면 망월리</t>
+          <t>인천광역시 강화군 선원면 금월리</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1012,12 +1012,12 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>1299094791</t>
+          <t>1147666750</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1299094791</t>
+          <t>https://m.place.naver.com/place/1147666750</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1034,24 +1034,24 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>맥스휘트니스클럽. 맥스PT샵</t>
+          <t>우리동네 헬스/PT</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>on180102@naver.com</t>
+          <t>wjddms0938@naver.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0507-1327-2830</t>
+          <t>032-937-9870</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 동문안길 9-1 4층</t>
+          <t>인천광역시 강화군 불은면 강화동로 587 1층</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1091,13 +1091,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="R7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="S7" t="inlineStr">
         <is>
@@ -1106,12 +1106,12 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>1506476586</t>
+          <t>2084651240</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1506476586</t>
+          <t>https://m.place.naver.com/place/2084651240</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1123,29 +1123,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>맥스 PT&amp;GT</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>topten0@naver.com</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
-          <t>070-8039-5423</t>
+          <t>0507-1407-5359</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 갑곳리</t>
+          <t>인천광역시 강화군 강화읍 동문안길 9-1 4층</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1188,10 +1188,10 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S8" t="inlineStr">
         <is>
@@ -1200,12 +1200,12 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>1533095100</t>
+          <t>1296569152</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1533095100</t>
+          <t>https://m.place.naver.com/place/1296569152</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
@@ -1217,29 +1217,29 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>에스오짐 1호점</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0507-1381-0814</t>
+          <t>070-8039-5432</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로 199 2층</t>
+          <t>인천광역시 강화군 하점면 망월리</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1279,13 +1279,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="S9" t="inlineStr">
         <is>
@@ -1294,12 +1294,12 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>1342561169</t>
+          <t>1299094791</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342561169</t>
+          <t>https://m.place.naver.com/place/1299094791</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
@@ -1311,30 +1311,34 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>에이스짐</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>acegym2@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>070-8039-5426</t>
+        </is>
+      </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 강화대로404번길 7 3층</t>
+          <t>인천광역시 강화군 불은면 고능리</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://instagram.com/ace__gym?igshid=ye2mgag95d7j</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1344,7 +1348,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1365,17 +1369,17 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="P10" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="S10" t="inlineStr">
         <is>
@@ -1384,12 +1388,12 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1768451605</t>
+          <t>1663184692</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1768451605</t>
+          <t>https://m.place.naver.com/place/1663184692</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
@@ -1401,34 +1405,34 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>피티아시바</t>
+          <t>몸짱휘트니스클럽</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>unixgaseol7@naver.com</t>
+          <t>byy333@naver.com</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>070-5255-2005</t>
+          <t>0507-1419-9688</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 선원면 금월리</t>
+          <t>인천광역시 강화군 선원면 중앙로 154 2충</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/byy333</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1438,12 +1442,12 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1463,13 +1467,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="S11" t="inlineStr">
         <is>
@@ -1478,12 +1482,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>1147666750</t>
+          <t>21494529</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1147666750</t>
+          <t>https://m.place.naver.com/place/21494529</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
@@ -1495,34 +1499,30 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>에이스짐</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>acegym2@naver.com</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>070-8039-5426</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 불은면 고능리</t>
+          <t>인천광역시 강화군 강화읍 강화대로404번길 7 3층</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/ace__gym?igshid=ye2mgag95d7j</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1532,7 +1532,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1553,17 +1553,17 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="S12" t="inlineStr">
         <is>
@@ -1572,12 +1572,12 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1663184692</t>
+          <t>1768451605</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1663184692</t>
+          <t>https://m.place.naver.com/place/1768451605</t>
         </is>
       </c>
       <c r="V12" t="inlineStr">
@@ -1589,29 +1589,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>스포츠시설</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>맥스 PT&amp;GT</t>
+          <t>스카이헬스클럽</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>topten0@naver.com</t>
+          <t>rokmc9160@naver.com</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0507-1407-5359</t>
+          <t>0507-1468-7831</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 동문안길 9-1 4층</t>
+          <t>인천광역시 강화군 강화읍 관청길23번길 8 관청길23번길8 스카이헬스클럽</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1651,13 +1651,13 @@
         </is>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="Q13" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="R13" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="S13" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1296569152</t>
+          <t>11847161</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1296569152</t>
+          <t>https://m.place.naver.com/place/11847161</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -1683,29 +1683,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>전문건설업</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>070-8055-2327</t>
+          <t>070-8039-5423</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 길상면 길직리</t>
+          <t>인천광역시 강화군 강화읍 갑곳리</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>1792485335</t>
+          <t>1533095100</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1792485335</t>
+          <t>https://m.place.naver.com/place/1533095100</t>
         </is>
       </c>
       <c r="V14" t="inlineStr">
@@ -1777,29 +1777,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>건축,토목</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>피티아시바</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>unixgaseol7@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>070-5255-6620</t>
+          <t>070-8039-5424</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 하점면 신봉리</t>
+          <t>인천광역시 강화군 길상면 길직리</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1854,12 +1854,12 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1018631235</t>
+          <t>1236022169</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1018631235</t>
+          <t>https://m.place.naver.com/place/1236022169</t>
         </is>
       </c>
       <c r="V15" t="inlineStr">
@@ -1871,29 +1871,29 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>건축,토목</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>피티아시바</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>unixgaseol7@naver.com</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>070-8039-5427</t>
+          <t>070-5255-6620</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 서도면 말도리</t>
+          <t>인천광역시 강화군 하점면 신봉리</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>1817432438</t>
+          <t>1018631235</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1817432438</t>
+          <t>https://m.place.naver.com/place/1018631235</t>
         </is>
       </c>
       <c r="V16" t="inlineStr">
@@ -1965,34 +1965,34 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>헬스장</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>에스오짐2호점</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>topten0@naver.com</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>070-8039-5428</t>
+          <t>032-934-2124</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 선원면 금월리</t>
+          <t>인천광역시 강화군 강화읍 중앙로 27 3층 S.O GYM 2호점</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://instagram.com/sogym_official2</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2023,17 +2023,17 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>139</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>151</v>
       </c>
       <c r="S17" t="inlineStr">
         <is>
@@ -2042,12 +2042,12 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>1944891267</t>
+          <t>1935773088</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1944891267</t>
+          <t>https://m.place.naver.com/place/1935773088</t>
         </is>
       </c>
       <c r="V17" t="inlineStr">
@@ -2059,34 +2059,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>스포츠시설</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>위너핏</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>boos66@naver.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>070-8039-5431</t>
+          <t>0507-1476-1622</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 양사면 교산리</t>
+          <t>인천광역시 강화군 강화읍 남문로 14 3층</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>https://blog.naver.com/boos66</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -2096,12 +2096,12 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -2117,17 +2117,17 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>X</t>
+          <t>O</t>
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>203</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>295</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>498</v>
       </c>
       <c r="S18" t="inlineStr">
         <is>
@@ -2136,12 +2136,12 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>1750263858</t>
+          <t>1895477243</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1750263858</t>
+          <t>https://m.place.naver.com/place/1895477243</t>
         </is>
       </c>
       <c r="V18" t="inlineStr">
@@ -2153,29 +2153,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>전문건설업</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>우리동네 헬스/PT</t>
+          <t>비티아시바피티아시바이동식비계가설재판매임대설치</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>subgymasan@naver.com</t>
+          <t>hnco@naver.com</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>032-937-9870</t>
+          <t>070-8055-2327</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 불은면 강화동로 587 1층</t>
+          <t>인천광역시 강화군 길상면 길직리</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2215,13 +2215,13 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="S19" t="inlineStr">
         <is>
@@ -2230,12 +2230,12 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2084651240</t>
+          <t>1792485335</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/2084651240</t>
+          <t>https://m.place.naver.com/place/1792485335</t>
         </is>
       </c>
       <c r="V19" t="inlineStr">
@@ -2247,29 +2247,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>장비,기기</t>
+          <t>소프트웨어개발</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
+          <t>비즈픽스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>hnco@naver.com</t>
+          <t>breezessol@naver.com</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>070-8039-5424</t>
+          <t>031-987-8937</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 길상면 길직리</t>
+          <t>경기도 김포시 월곶면 김포대학로 22</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2324,12 +2324,12 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>1236022169</t>
+          <t>1342017021</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1236022169</t>
+          <t>https://m.place.naver.com/place/1342017021</t>
         </is>
       </c>
       <c r="V20" t="inlineStr">
@@ -2341,29 +2341,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>스카이헬스클럽</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>rokmc9160@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0507-1468-7831</t>
+          <t>070-8039-5428</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 강화읍 관청길23번길 8 관청길23번길8 스카이헬스클럽</t>
+          <t>인천광역시 강화군 선원면 금월리</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2403,13 +2403,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="S21" t="inlineStr">
         <is>
@@ -2418,12 +2418,12 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>11847161</t>
+          <t>1944891267</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/11847161</t>
+          <t>https://m.place.naver.com/place/1944891267</t>
         </is>
       </c>
       <c r="V21" t="inlineStr">
@@ -2435,29 +2435,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>소프트웨어개발</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>비즈픽스</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>breezessol@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>031-987-8937</t>
+          <t>070-8039-5431</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>경기도 김포시 월곶면 김포대학로 22</t>
+          <t>인천광역시 강화군 양사면 교산리</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2512,12 +2512,12 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>1342017021</t>
+          <t>1750263858</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/1342017021</t>
+          <t>https://m.place.naver.com/place/1750263858</t>
         </is>
       </c>
       <c r="V22" t="inlineStr">
@@ -2529,34 +2529,34 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>헬스장</t>
+          <t>장비,기기</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>몸짱휘트니스클럽</t>
+          <t>드림,BT,아시바,빌려주는곳,비티,PT,피티,아시바,가설,비계,대여,임대</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>byy333@naver.com</t>
+          <t>eventheo@naver.com</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
       <c r="E23" t="inlineStr">
         <is>
-          <t>0507-1419-9688</t>
+          <t>070-8039-5429</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>인천광역시 강화군 선원면 중앙로 154 2충</t>
+          <t>인천광역시 강화군 송해면 당산리</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://blog.naver.com/byy333</t>
+          <t>X</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>O</t>
+          <t>X</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2591,13 +2591,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="S23" t="inlineStr">
         <is>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>21494529</t>
+          <t>1877492123</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
         <is>
-          <t>https://m.place.naver.com/place/21494529</t>
+          <t>https://m.place.naver.com/place/1877492123</t>
         </is>
       </c>
       <c r="V23" t="inlineStr">
